--- a/artfynd/A 53664-2025 artfynd.xlsx
+++ b/artfynd/A 53664-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4749,6 +4749,220 @@
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129996520</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78841</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>475201</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6831084</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129996518</v>
+      </c>
+      <c r="B41" t="n">
+        <v>78842</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>475311</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6831135</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53664-2025 artfynd.xlsx
+++ b/artfynd/A 53664-2025 artfynd.xlsx
@@ -4754,7 +4754,7 @@
         <v>129996520</v>
       </c>
       <c r="B40" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>129996518</v>
       </c>
       <c r="B41" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 53664-2025 artfynd.xlsx
+++ b/artfynd/A 53664-2025 artfynd.xlsx
@@ -4754,7 +4754,7 @@
         <v>129996520</v>
       </c>
       <c r="B40" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>129996518</v>
       </c>
       <c r="B41" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 53664-2025 artfynd.xlsx
+++ b/artfynd/A 53664-2025 artfynd.xlsx
@@ -4754,7 +4754,7 @@
         <v>129996520</v>
       </c>
       <c r="B40" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>129996518</v>
       </c>
       <c r="B41" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 53664-2025 artfynd.xlsx
+++ b/artfynd/A 53664-2025 artfynd.xlsx
@@ -4754,7 +4754,7 @@
         <v>129996520</v>
       </c>
       <c r="B40" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>129996518</v>
       </c>
       <c r="B41" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
